--- a/data/availability/projects/emaar-misr/soul.xlsx
+++ b/data/availability/projects/emaar-misr/soul.xlsx
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>31/12/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1709,7 +1709,6 @@
       <c r="G2" t="n">
         <v>125.3</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1766,7 +1765,6 @@
       <c r="G3" t="n">
         <v>690.9</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1823,7 +1821,6 @@
       <c r="G4" t="n">
         <v>379.4</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1880,7 +1877,6 @@
       <c r="G5" t="n">
         <v>381</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1937,7 +1933,6 @@
       <c r="G6" t="n">
         <v>381</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1994,7 +1989,6 @@
       <c r="G7" t="n">
         <v>493.9</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2051,7 +2045,6 @@
       <c r="G8" t="n">
         <v>552.7</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2108,7 +2101,6 @@
       <c r="G9" t="n">
         <v>504.1</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2165,7 +2157,6 @@
       <c r="G10" t="n">
         <v>497.6</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2176,7 +2167,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2222,7 +2213,6 @@
       <c r="G11" t="n">
         <v>612.4</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2233,7 +2223,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2279,7 +2269,6 @@
       <c r="G12" t="n">
         <v>580.7</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2290,7 +2279,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2336,7 +2325,6 @@
       <c r="G13" t="n">
         <v>451.5</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2347,7 +2335,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2393,7 +2381,6 @@
       <c r="G14" t="n">
         <v>454.9</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2450,7 +2437,6 @@
       <c r="G15" t="n">
         <v>590.3</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2461,7 +2447,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2507,7 +2493,6 @@
       <c r="G16" t="n">
         <v>416</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2564,7 +2549,6 @@
       <c r="G17" t="n">
         <v>566.8</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2621,7 +2605,6 @@
       <c r="G18" t="n">
         <v>485.7</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2632,7 +2615,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2678,7 +2661,6 @@
       <c r="G19" t="n">
         <v>485.7</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2689,7 +2671,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2735,7 +2717,6 @@
       <c r="G20" t="n">
         <v>492.9</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2746,7 +2727,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2792,7 +2773,6 @@
       <c r="G21" t="n">
         <v>508</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2803,7 +2783,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31/03/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2849,7 +2829,6 @@
       <c r="G22" t="n">
         <v>580.6</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2906,7 +2885,6 @@
       <c r="G23" t="n">
         <v>580.5</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2963,7 +2941,6 @@
       <c r="G24" t="n">
         <v>580.5</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3020,7 +2997,6 @@
       <c r="G25" t="n">
         <v>467.6</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3077,7 +3053,6 @@
       <c r="G26" t="n">
         <v>581</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3134,7 +3109,6 @@
       <c r="G27" t="n">
         <v>542.5</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3191,7 +3165,6 @@
       <c r="G28" t="n">
         <v>374.1</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3248,7 +3221,6 @@
       <c r="G29" t="n">
         <v>388.6</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3305,7 +3277,6 @@
       <c r="G30" t="n">
         <v>377.6</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3362,7 +3333,6 @@
       <c r="G31" t="n">
         <v>375.6</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3419,7 +3389,6 @@
       <c r="G32" t="n">
         <v>372.8</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3476,7 +3445,6 @@
       <c r="G33" t="n">
         <v>550.8</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3533,7 +3501,6 @@
       <c r="G34" t="n">
         <v>532.3</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3590,7 +3557,6 @@
       <c r="G35" t="n">
         <v>535.1</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3647,7 +3613,6 @@
       <c r="G36" t="n">
         <v>460.2</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3704,7 +3669,6 @@
       <c r="G37" t="n">
         <v>478.9</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3761,7 +3725,6 @@
       <c r="G38" t="n">
         <v>601.7</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3772,7 +3735,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3818,7 +3781,6 @@
       <c r="G39" t="n">
         <v>349.4</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3829,7 +3791,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3875,7 +3837,6 @@
       <c r="G40" t="n">
         <v>382.1</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3886,7 +3847,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3932,7 +3893,6 @@
       <c r="G41" t="n">
         <v>382.4</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3943,7 +3903,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3989,7 +3949,6 @@
       <c r="G42" t="n">
         <v>382</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4000,7 +3959,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4046,7 +4005,6 @@
       <c r="G43" t="n">
         <v>382</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4057,7 +4015,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4103,7 +4061,6 @@
       <c r="G44" t="n">
         <v>381.9</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4114,7 +4071,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4160,7 +4117,6 @@
       <c r="G45" t="n">
         <v>381.8</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4171,7 +4127,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4217,7 +4173,6 @@
       <c r="G46" t="n">
         <v>442.9</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4228,7 +4183,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4274,7 +4229,6 @@
       <c r="G47" t="n">
         <v>462.2</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4285,7 +4239,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4331,7 +4285,6 @@
       <c r="G48" t="n">
         <v>475.8</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4342,7 +4295,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>31/07/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4388,7 +4341,6 @@
       <c r="G49" t="n">
         <v>393.2</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4445,7 +4397,6 @@
       <c r="G50" t="n">
         <v>380.6</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4502,7 +4453,6 @@
       <c r="G51" t="n">
         <v>348.5</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4559,7 +4509,6 @@
       <c r="G52" t="n">
         <v>382.2</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4616,7 +4565,6 @@
       <c r="G53" t="n">
         <v>407.6</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4673,7 +4621,6 @@
       <c r="G54" t="n">
         <v>347.8</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4730,7 +4677,6 @@
       <c r="G55" t="n">
         <v>173</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4741,7 +4687,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>31/12/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4787,7 +4733,6 @@
       <c r="G56" t="n">
         <v>173</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4798,7 +4743,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>31/12/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4844,7 +4789,6 @@
       <c r="G57" t="n">
         <v>259.9</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4855,7 +4799,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4901,7 +4845,6 @@
       <c r="G58" t="n">
         <v>262</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4912,7 +4855,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4958,7 +4901,6 @@
       <c r="G59" t="n">
         <v>163.8</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4969,7 +4911,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5015,7 +4957,6 @@
       <c r="G60" t="n">
         <v>256.2</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5026,7 +4967,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5072,7 +5013,6 @@
       <c r="G61" t="n">
         <v>163.8</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5083,7 +5023,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5129,7 +5069,6 @@
       <c r="G62" t="n">
         <v>377.4</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5140,7 +5079,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5186,7 +5125,6 @@
       <c r="G63" t="n">
         <v>174.8</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5197,7 +5135,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5243,7 +5181,6 @@
       <c r="G64" t="n">
         <v>371.4</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5254,7 +5191,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5300,7 +5237,6 @@
       <c r="G65" t="n">
         <v>375.3</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5311,7 +5247,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5357,7 +5293,6 @@
       <c r="G66" t="n">
         <v>504.2</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5368,7 +5303,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5414,7 +5349,6 @@
       <c r="G67" t="n">
         <v>543.5</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5425,7 +5359,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5471,7 +5405,6 @@
       <c r="G68" t="n">
         <v>608.3</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5482,7 +5415,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5528,7 +5461,6 @@
       <c r="G69" t="n">
         <v>519</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5539,7 +5471,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5585,7 +5517,6 @@
       <c r="G70" t="n">
         <v>377.2</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5596,7 +5527,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5642,7 +5573,6 @@
       <c r="G71" t="n">
         <v>437.3</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5653,7 +5583,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5699,7 +5629,6 @@
       <c r="G72" t="n">
         <v>397.9</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5710,7 +5639,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5756,7 +5685,6 @@
       <c r="G73" t="n">
         <v>425.8</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5767,7 +5695,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5813,7 +5741,6 @@
       <c r="G74" t="n">
         <v>415</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5824,7 +5751,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5870,7 +5797,6 @@
       <c r="G75" t="n">
         <v>588.5</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5881,7 +5807,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5927,7 +5853,6 @@
       <c r="G76" t="n">
         <v>569.4</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5938,7 +5863,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5984,7 +5909,6 @@
       <c r="G77" t="n">
         <v>591.8</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5995,7 +5919,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6041,7 +5965,6 @@
       <c r="G78" t="n">
         <v>529.1</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6052,7 +5975,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6098,7 +6021,6 @@
       <c r="G79" t="n">
         <v>426.7</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6109,7 +6031,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6155,7 +6077,6 @@
       <c r="G80" t="n">
         <v>513.1</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6166,7 +6087,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6212,7 +6133,6 @@
       <c r="G81" t="n">
         <v>357.2</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6223,7 +6143,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6269,7 +6189,6 @@
       <c r="G82" t="n">
         <v>357.6</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6280,7 +6199,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6326,7 +6245,6 @@
       <c r="G83" t="n">
         <v>173.5</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6337,7 +6255,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6383,7 +6301,6 @@
       <c r="G84" t="n">
         <v>166.9</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6394,7 +6311,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6440,7 +6357,6 @@
       <c r="G85" t="n">
         <v>320.3</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6451,7 +6367,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6497,7 +6413,6 @@
       <c r="G86" t="n">
         <v>168.8</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6508,7 +6423,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6554,7 +6469,6 @@
       <c r="G87" t="n">
         <v>170</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6565,7 +6479,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>31/08/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
